--- a/survey_templates/030_nicu_resuscitation_feedback_survey--survey_templates.xlsx
+++ b/survey_templates/030_nicu_resuscitation_feedback_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -742,8 +742,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -771,12 +771,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'cardiac_arrest'}</t>
+          <t>cardiac_arrest</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Cardiac Arrest'}</t>
+          <t>Cardiac Arrest</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'seizure'}</t>
+          <t>seizure</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Seizure'}</t>
+          <t>Seizure</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -822,12 +822,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'doctor'}</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Doctor'}</t>
+          <t>Doctor</t>
         </is>
       </c>
     </row>
@@ -839,12 +839,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'nurse'}</t>
+          <t>nurse</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Nurse'}</t>
+          <t>Nurse</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'respiratory'}</t>
+          <t>respiratory</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Respiratory'}</t>
+          <t>Respiratory</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -890,12 +890,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'cpap'}</t>
+          <t>cpap</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'CPAP'}</t>
+          <t>CPAP</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'ppv'}</t>
+          <t>ppv</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'PPV'}</t>
+          <t>PPV</t>
         </is>
       </c>
     </row>
@@ -924,12 +924,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'hypotension'}</t>
+          <t>hypotension</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Hypotension'}</t>
+          <t>Hypotension</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'hypertension'}</t>
+          <t>hypertension</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Hypertension'}</t>
+          <t>Hypertension</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'hypoxia'}</t>
+          <t>hypoxia</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Hypoxia'}</t>
+          <t>Hypoxia</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'bradycardia'}</t>
+          <t>bradycardia</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Bradycardia'}</t>
+          <t>Bradycardia</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
